--- a/assets-source/icons/ICON_CATALOG.xlsx
+++ b/assets-source/icons/ICON_CATALOG.xlsx
@@ -6872,7 +6872,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>26</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -6897,7 +6897,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>34</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -6922,7 +6922,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>28</row>
+      <row>35</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -6947,7 +6947,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>29</row>
+      <row>36</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -6972,7 +6972,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>30</row>
+      <row>37</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -6997,7 +6997,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>31</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7022,7 +7022,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7047,7 +7047,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>40</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7072,7 +7072,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7097,7 +7097,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>35</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7122,7 +7122,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7147,7 +7147,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>37</row>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7172,7 +7172,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>38</row>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7197,7 +7197,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7222,7 +7222,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>59</row>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7247,7 +7247,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>60</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7272,7 +7272,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>61</row>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7297,7 +7297,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>62</row>
+      <row>50</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7322,7 +7322,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>63</row>
+      <row>51</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7347,7 +7347,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>52</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7372,7 +7372,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>65</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7397,7 +7397,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>66</row>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7422,7 +7422,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>67</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7447,7 +7447,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>68</row>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7472,7 +7472,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>69</row>
+      <row>57</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7497,7 +7497,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>70</row>
+      <row>58</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7522,7 +7522,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7547,7 +7547,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>72</row>
+      <row>60</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7572,7 +7572,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>61</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7597,7 +7597,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7622,7 +7622,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>94</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7647,7 +7647,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>95</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7672,7 +7672,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>96</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7697,7 +7697,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>97</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7722,7 +7722,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7747,7 +7747,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>99</row>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7772,7 +7772,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>100</row>
+      <row>96</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7797,7 +7797,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7822,7 +7822,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>102</row>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7847,7 +7847,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>103</row>
+      <row>99</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7872,7 +7872,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>104</row>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7897,7 +7897,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>105</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7922,7 +7922,1087 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>125</row>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>92</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>93</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>95</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>96</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>98</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>100</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7947,7 +9027,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>126</row>
+      <row>101</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7972,7 +9052,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>127</row>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -7997,7 +9077,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>128</row>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8022,7 +9102,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>129</row>
+      <row>104</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8047,7 +9127,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>130</row>
+      <row>105</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8072,7 +9152,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>131</row>
+      <row>125</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8097,7 +9177,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>132</row>
+      <row>126</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8122,7 +9202,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>133</row>
+      <row>127</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8147,7 +9227,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>134</row>
+      <row>128</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8172,7 +9252,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>135</row>
+      <row>129</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8197,7 +9277,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>136</row>
+      <row>130</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8222,7 +9302,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>137</row>
+      <row>131</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8247,7 +9327,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>138</row>
+      <row>132</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8272,7 +9352,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>158</row>
+      <row>133</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8297,7 +9377,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>159</row>
+      <row>134</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8322,7 +9402,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>160</row>
+      <row>135</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8347,7 +9427,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>161</row>
+      <row>136</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8372,7 +9452,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>162</row>
+      <row>137</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8397,7 +9477,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>163</row>
+      <row>138</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8422,7 +9502,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>164</row>
+      <row>158</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8447,7 +9527,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>165</row>
+      <row>159</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8472,7 +9552,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>166</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8497,7 +9577,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>167</row>
+      <row>161</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8522,7 +9602,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>168</row>
+      <row>162</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8547,7 +9627,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>169</row>
+      <row>163</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8572,7 +9652,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>170</row>
+      <row>164</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8597,7 +9677,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>171</row>
+      <row>165</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8622,7 +9702,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>191</row>
+      <row>166</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8647,7 +9727,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>192</row>
+      <row>167</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8672,7 +9752,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>193</row>
+      <row>168</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8697,7 +9777,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>194</row>
+      <row>169</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8722,7 +9802,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>195</row>
+      <row>170</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8747,7 +9827,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>196</row>
+      <row>171</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8772,7 +9852,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>197</row>
+      <row>191</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8797,7 +9877,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>198</row>
+      <row>192</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8822,7 +9902,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>199</row>
+      <row>193</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8847,7 +9927,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>200</row>
+      <row>194</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8872,7 +9952,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>201</row>
+      <row>195</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8897,7 +9977,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>202</row>
+      <row>196</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8922,7 +10002,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>203</row>
+      <row>197</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8947,7 +10027,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>204</row>
+      <row>198</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8972,7 +10052,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>205</row>
+      <row>199</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -8997,7 +10077,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>206</row>
+      <row>200</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9022,7 +10102,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>207</row>
+      <row>201</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9047,7 +10127,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>208</row>
+      <row>202</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9072,7 +10152,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>209</row>
+      <row>203</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9097,7 +10177,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>210</row>
+      <row>204</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9122,7 +10202,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>211</row>
+      <row>205</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9147,7 +10227,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>212</row>
+      <row>206</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9172,7 +10252,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>213</row>
+      <row>207</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9197,7 +10277,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>214</row>
+      <row>208</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9222,7 +10302,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>215</row>
+      <row>209</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9247,7 +10327,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>216</row>
+      <row>210</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9272,7 +10352,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>217</row>
+      <row>211</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9297,7 +10377,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>218</row>
+      <row>212</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9322,7 +10402,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>219</row>
+      <row>213</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9347,7 +10427,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>220</row>
+      <row>214</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9372,7 +10452,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>221</row>
+      <row>215</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9397,7 +10477,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>222</row>
+      <row>216</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9422,7 +10502,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>223</row>
+      <row>217</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9447,7 +10527,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>224</row>
+      <row>218</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9472,7 +10552,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>225</row>
+      <row>219</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9497,7 +10577,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>226</row>
+      <row>220</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9522,7 +10602,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>227</row>
+      <row>221</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9547,7 +10627,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>228</row>
+      <row>222</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9572,7 +10652,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>229</row>
+      <row>223</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9597,7 +10677,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>230</row>
+      <row>224</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9622,7 +10702,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>231</row>
+      <row>225</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9647,7 +10727,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>232</row>
+      <row>226</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9672,7 +10752,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>233</row>
+      <row>227</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9697,7 +10777,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>234</row>
+      <row>228</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9722,7 +10802,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>235</row>
+      <row>229</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9747,7 +10827,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>236</row>
+      <row>230</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9772,7 +10852,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>237</row>
+      <row>231</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9797,7 +10877,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>238</row>
+      <row>232</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9822,7 +10902,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>239</row>
+      <row>233</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9847,7 +10927,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>240</row>
+      <row>234</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9872,7 +10952,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>241</row>
+      <row>235</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9897,7 +10977,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>242</row>
+      <row>236</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9922,7 +11002,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>243</row>
+      <row>237</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9947,7 +11027,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>244</row>
+      <row>238</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9972,7 +11052,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>245</row>
+      <row>239</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -9997,7 +11077,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>246</row>
+      <row>240</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -10022,7 +11102,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>247</row>
+      <row>241</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -10047,7 +11127,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>248</row>
+      <row>242</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="381000"/>
@@ -10058,6 +11138,156 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId128"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>243</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="129" name="Image 129" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId129"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>244</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="130" name="Image 130" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId130"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>245</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="131" name="Image 131" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId131"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>246</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="132" name="Image 132" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId132"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>247</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="133" name="Image 133" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId133"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>248</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="134" name="Image 134" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId134"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -10377,7 +11607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated by npm run icons:catalog from content content-0.8.0 on 2026-10-02. One sheet per section; the Status column is yours (it is not overwritten when you keep your own copy).</t>
+          <t>Generated by npm run icons:catalog from content content-0.8.0 on 2026-10-03. One sheet per section; the Status column is yours (it is not overwritten when you keep your own copy).</t>
         </is>
       </c>
     </row>
@@ -20261,7 +21491,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier1.base.portrait.webp</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
@@ -20311,7 +21541,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier1.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -20361,7 +21591,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier2.base.portrait.webp</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
@@ -20411,7 +21641,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier2.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -20461,7 +21691,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier3.base.portrait.webp</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
@@ -20511,7 +21741,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier3.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -20561,7 +21791,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier4.base.portrait.webp</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
@@ -20611,7 +21841,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier4.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -20661,7 +21891,7 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier5.base.portrait.webp</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -20711,7 +21941,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier5.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
@@ -20761,7 +21991,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier6.base.portrait.webp</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
@@ -20811,7 +22041,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier6.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
@@ -20861,7 +22091,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier7.base.portrait.webp</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
@@ -20911,7 +22141,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.egyptian.tier7.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -20961,7 +22191,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier1.base.portrait.webp</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -21011,7 +22241,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier1.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
@@ -21061,7 +22291,7 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier2.base.portrait.webp</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
@@ -21111,7 +22341,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier2.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
@@ -21161,7 +22391,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier3.base.portrait.webp</t>
         </is>
       </c>
       <c r="H52" s="5" t="inlineStr">
@@ -21211,7 +22441,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier3.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -21261,7 +22491,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier4.base.portrait.webp</t>
         </is>
       </c>
       <c r="H54" s="5" t="inlineStr">
@@ -21311,7 +22541,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier4.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
@@ -21361,7 +22591,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier5.base.portrait.webp</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
@@ -21411,7 +22641,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier5.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
@@ -21461,7 +22691,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier6.base.portrait.webp</t>
         </is>
       </c>
       <c r="H58" s="5" t="inlineStr">
@@ -21511,7 +22741,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier6.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H59" s="5" t="inlineStr">
@@ -21561,7 +22791,7 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier7.base.portrait.webp</t>
         </is>
       </c>
       <c r="H60" s="5" t="inlineStr">
@@ -21611,7 +22841,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.greek.tier7.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
@@ -21661,7 +22891,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.japanese.tier1.base.portrait.webp</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
@@ -23061,7 +24291,7 @@
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier1.base.portrait.webp</t>
         </is>
       </c>
       <c r="H90" s="5" t="inlineStr">
@@ -23111,7 +24341,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier1.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H91" s="5" t="inlineStr">
@@ -23161,7 +24391,7 @@
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier2.base.portrait.webp</t>
         </is>
       </c>
       <c r="H92" s="5" t="inlineStr">
@@ -23211,7 +24441,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier2.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H93" s="5" t="inlineStr">
@@ -23261,7 +24491,7 @@
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier3.base.portrait.webp</t>
         </is>
       </c>
       <c r="H94" s="5" t="inlineStr">
@@ -23311,7 +24541,7 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier3.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H95" s="5" t="inlineStr">
@@ -23361,7 +24591,7 @@
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier4.base.portrait.webp</t>
         </is>
       </c>
       <c r="H96" s="5" t="inlineStr">
@@ -23411,7 +24641,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier4.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H97" s="5" t="inlineStr">
@@ -23461,7 +24691,7 @@
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier5.base.portrait.webp</t>
         </is>
       </c>
       <c r="H98" s="5" t="inlineStr">
@@ -23511,7 +24741,7 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier5.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H99" s="5" t="inlineStr">
@@ -23561,7 +24791,7 @@
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier6.base.portrait.webp</t>
         </is>
       </c>
       <c r="H100" s="5" t="inlineStr">
@@ -23611,7 +24841,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier6.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H101" s="5" t="inlineStr">
@@ -23661,7 +24891,7 @@
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier7.base.portrait.webp</t>
         </is>
       </c>
       <c r="H102" s="5" t="inlineStr">
@@ -23711,7 +24941,7 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/creature.norse.tier7.upgraded.portrait.webp</t>
         </is>
       </c>
       <c r="H103" s="5" t="inlineStr">
@@ -23740,6 +24970,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -23857,7 +25088,7 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/emblem.greek.png</t>
         </is>
       </c>
       <c r="H2" s="5" t="inlineStr">
@@ -23907,7 +25138,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/emblem.norse.png</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
@@ -23957,7 +25188,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/emblem.egyptian.png</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -24007,7 +25238,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/emblem.japanese.png</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
@@ -24057,7 +25288,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/emblem.celtic.png</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -24107,7 +25338,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Generated placeholder / text — generated placeholder</t>
+          <t>Final art — assets-runtime/ui/icons/final/emblem.mesoamerican.png</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -36167,7 +37398,7 @@
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Kingdom overview</t>
+          <t>Adventure map; Dialogs (briefing, debrief, pause, save/load, encounters); Kingdom overview</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -36293,7 +37524,7 @@
       <c r="E28" s="2" t="inlineStr"/>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Dialogs (briefing, debrief, pause, save/load, encounters); Main menu; Recruitment</t>
+          <t>Adventure map; Dialogs (briefing, debrief, pause, save/load, encounters); Encyclopedia; Main menu; Recruitment</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -36545,7 +37776,7 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Dialogs (briefing, debrief, pause, save/load, encounters); Hero screen; New game / setup; Random map setup; Results / high scores; Shared game widgets (resource bar, costs, stat blocks)</t>
+          <t>Dialogs (briefing, debrief, pause, save/load, encounters); Hero screen; New game / setup; Results / high scores; Shared game widgets (resource bar, costs, stat blocks)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -36629,7 +37860,7 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Battle; Creature detail; Dialogs (briefing, debrief, pause, save/load, encounters)</t>
+          <t>Battle; Creature detail; Dialogs (briefing, debrief, pause, save/load, encounters); Random map setup</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -37091,7 +38322,7 @@
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Battle</t>
+          <t>Battle; Dialogs (briefing, debrief, pause, save/load, encounters)</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -37385,7 +38616,7 @@
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Ability badge stand-in (army slots, creature details, encyclopedia) until the ability icon exists; Hero screen; Town</t>
+          <t>Ability badge stand-in (army slots, creature details, encyclopedia) until the ability icon exists; Hero screen</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -37511,7 +38742,7 @@
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Main menu; New game / setup</t>
+          <t>New game / setup</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -37595,7 +38826,7 @@
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Artifact fallback glyph (hero screen, merchant, encyclopedia); Hero screen; Main menu; Results / high scores; Shared art widgets</t>
+          <t>Artifact fallback glyph (hero screen, merchant, encyclopedia); Hero screen; Results / high scores; Shared art widgets</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">

--- a/assets-source/icons/ICON_CATALOG.xlsx
+++ b/assets-source/icons/ICON_CATALOG.xlsx
@@ -22,7 +22,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Emblems, buildings and thumbnai" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interface icons'!$A$1:$L$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Interface icons'!$A$1:$L$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Map markers'!$A$1:$L$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Spells'!$A$1:$L$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Artifacts'!$A$1:$L$80</definedName>
@@ -1673,6 +1673,156 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="381000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -11703,7 +11853,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>60 / 0 / 96 × 96 px PNG, transparent (menu icons 192 px)</t>
+          <t>66 / 6 / 96 × 96 px PNG, transparent (menu icons 192 px)</t>
         </is>
       </c>
     </row>
@@ -36333,7 +36483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -36432,7 +36582,7 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Costs and rewards (every screen); Kingdom overview; Resource bar (adventure, town); Town</t>
+          <t>Costs and rewards (every screen); Resource bar (adventure, town)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -36768,7 +36918,7 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Ability badge stand-in (army slots, creature details, encyclopedia) until the ability icon exists; Adventure map; Artifact fallback glyph (hero screen, merchant, encyclopedia); Battle; Encyclopedia; Hero screen</t>
+          <t>Ability badge stand-in (army slots, creature details, encyclopedia) until the ability icon exists; Artifact fallback glyph (hero screen, merchant, encyclopedia); Battle; Encyclopedia; Hero screen</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -37020,7 +37170,7 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Map dialogs (camps, events, sites)</t>
+          <t>Map dialogs (camps, events, sites); Town</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -37062,7 +37212,7 @@
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Artifact fallback glyph (hero screen, merchant, encyclopedia); Hero screen</t>
+          <t>Artifact fallback glyph (hero screen, merchant, encyclopedia); Hero screen</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -37104,7 +37254,7 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Hero screen</t>
+          <t>Hero screen</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -37230,7 +37380,7 @@
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Artifact fallback glyph (hero screen, merchant, encyclopedia); Hero screen</t>
+          <t>Artifact fallback glyph (hero screen, merchant, encyclopedia); Hero screen</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -37272,7 +37422,7 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Artifact fallback glyph (hero screen, merchant, encyclopedia); Hero screen</t>
+          <t>Artifact fallback glyph (hero screen, merchant, encyclopedia); Hero screen</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -37314,7 +37464,7 @@
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Hero screen</t>
+          <t>Hero screen; Town</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -37356,7 +37506,7 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Kingdom overview; Town</t>
+          <t>Adventure map</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -37398,7 +37548,7 @@
       <c r="E25" s="2" t="inlineStr"/>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Dialogs (briefing, debrief, pause, save/load, encounters); Kingdom overview</t>
+          <t>Adventure map; Dialogs (briefing, debrief, pause, save/load, encounters); Town</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -37482,7 +37632,7 @@
       <c r="E27" s="2" t="inlineStr"/>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Adventure map</t>
+          <t>(not shown on any screen yet)</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -37566,7 +37716,7 @@
       <c r="E29" s="2" t="inlineStr"/>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Kingdom overview; Pantheon; Town</t>
+          <t>Adventure map; Pantheon; Town</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -37776,7 +37926,7 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Dialogs (briefing, debrief, pause, save/load, encounters); Hero screen; New game / setup; Results / high scores; Shared game widgets (resource bar, costs, stat blocks)</t>
+          <t>Dialogs (briefing, debrief, pause, save/load, encounters); New game / setup; Results / high scores; Shared game widgets (resource bar, costs, stat blocks)</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -37818,7 +37968,7 @@
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Battle; Journal; Shared controls (every screen)</t>
+          <t>Adventure map; Battle; Journal; Shared controls (every screen); Town</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -37986,7 +38136,7 @@
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Ability badge stand-in (army slots, creature details, encyclopedia) until the ability icon exists; Hero screen; Main menu</t>
+          <t>Ability badge stand-in (army slots, creature details, encyclopedia) until the ability icon exists; Main menu</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -38070,7 +38220,7 @@
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Main menu; New game / setup</t>
+          <t>New game / setup</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -38112,7 +38262,7 @@
       <c r="E42" s="2" t="inlineStr"/>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Main menu; New game / setup</t>
+          <t>New game / setup</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -38154,7 +38304,7 @@
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Dialogs (briefing, debrief, pause, save/load, encounters); Main menu</t>
+          <t>Main menu</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -38196,7 +38346,7 @@
       <c r="E44" s="2" t="inlineStr"/>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Main menu</t>
+          <t>(not shown on any screen yet)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -38364,7 +38514,7 @@
       <c r="E48" s="2" t="inlineStr"/>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Battle; Hero screen</t>
+          <t>Adventure map; Battle; Hero screen; Town</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -38448,7 +38598,7 @@
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Ability badge stand-in (army slots, creature details, encyclopedia) until the ability icon exists</t>
+          <t>Ability badge stand-in (army slots, creature details, encyclopedia) until the ability icon exists; Town</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -38616,7 +38766,7 @@
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Ability badge stand-in (army slots, creature details, encyclopedia) until the ability icon exists; Hero screen</t>
+          <t>Ability badge stand-in (army slots, creature details, encyclopedia) until the ability icon exists; Hero screen; Town</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -38658,7 +38808,7 @@
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Journal; Kingdom overview</t>
+          <t>Adventure map; Journal</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -38700,7 +38850,7 @@
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Adventure map; Hero screen; Journal; Kingdom overview</t>
+          <t>Adventure map; Hero screen; Journal</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -38826,7 +38976,7 @@
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Artifact fallback glyph (hero screen, merchant, encyclopedia); Hero screen; Results / high scores; Shared art widgets</t>
+          <t>Artifact fallback glyph (hero screen, merchant, encyclopedia); Hero screen; Journal; Results / high scores; Shared art widgets</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -38932,10 +39082,286 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
     </row>
+    <row r="62" ht="34" customHeight="1">
+      <c r="A62" s="2" t="n"/>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>icon.ui.build</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>build</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr"/>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>SVG glyph — glyph 'build'</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>now</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Build (town pop-up and build-today mark) — a builder’s hammer.</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr"/>
+      <c r="K62" s="5" t="inlineStr"/>
+      <c r="L62" s="5" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="34" customHeight="1">
+      <c r="A63" s="2" t="n"/>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>icon.ui.recruit</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>recruit</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr"/>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>SVG glyph — glyph 'recruit'</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>now</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Recruit troops — a crested helmet over a small banner.</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr"/>
+      <c r="K63" s="5" t="inlineStr"/>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="34" customHeight="1">
+      <c r="A64" s="2" t="n"/>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>icon.ui.market</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr"/>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>SVG glyph — glyph 'market'</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>now</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Marketplace / trade resources — a balance scale.</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr"/>
+      <c r="K64" s="5" t="inlineStr"/>
+      <c r="L64" s="5" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" s="2" t="n"/>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>icon.ui.tavern</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>tavern</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr"/>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>SVG glyph — glyph 'tavern'</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>now</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Tavern / hire heroes — a foaming tankard.</t>
+        </is>
+      </c>
+      <c r="J65" s="5" t="inlineStr"/>
+      <c r="K65" s="5" t="inlineStr"/>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="34" customHeight="1">
+      <c r="A66" s="2" t="n"/>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>icon.ui.merchant</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>merchant</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr"/>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="inlineStr">
+        <is>
+          <t>SVG glyph — glyph 'merchant'</t>
+        </is>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>now</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Artifact Merchant — a coin pouch with a gem.</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr"/>
+      <c r="K66" s="5" t="inlineStr"/>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="2" t="n"/>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>icon.ui.gift</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>gift</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Interface</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr"/>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="inlineStr">
+        <is>
+          <t>SVG glyph — glyph 'gift'</t>
+        </is>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>now</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Divine gifts — a wrapped offering box with a ribbon.</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr"/>
+      <c r="K67" s="5" t="inlineStr"/>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>To do</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L61"/>
+  <autoFilter ref="A1:L67"/>
   <dataValidations count="1">
-    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"To do,In progress,Review,Done"</formula1>
     </dataValidation>
   </dataValidations>
